--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -445,70 +445,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>uid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pincode</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>contact_no</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>contact_email</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>contact_person</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>vendor_uid</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>outlet_status</t>
         </is>
       </c>
     </row>
@@ -524,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -552,7 +558,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,14 +568,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>Customer Code — the key that decides update vs. create. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>uid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,14 +585,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>Store UID. Mandatory, and unique across all stores.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -596,14 +602,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -613,14 +619,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latitude (decimal).</t>
+          <t>Full store address.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -630,92 +636,109 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Longitude (decimal).</t>
+          <t>PIN code.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Store UID — used as the de-dupe key on re-upload.</t>
+          <t>Latitude (decimal), between -90 and 90.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>long</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact email.</t>
+          <t>Store contact phone.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact person.</t>
+          <t>Store contact email. Must be a valid address.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Store contact person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>outlet_status</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Vendor this store belongs to (must exist), e.g. VND-001.</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Outlet status from the customer master, e.g. ACTIVE.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -455,10 +455,9 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,50 +468,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>contact_person</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>outlet_status</t>
         </is>
@@ -530,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -568,14 +562,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Code — the key that decides update vs. create. Must be unique.</t>
+          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,14 +579,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store UID. Mandatory, and unique across all stores.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -602,14 +596,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>Full store address.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>pincode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -619,14 +613,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>PIN code.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>lat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,14 +630,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Latitude (decimal), between -90 and 90.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>long</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,14 +647,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latitude (decimal), between -90 and 90.</t>
+          <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>contact_no</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,14 +664,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Longitude (decimal), between -180 and 180.</t>
+          <t>Store contact phone.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -687,14 +681,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Store contact email. Must be a valid address.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -704,39 +698,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact email. Must be a valid address.</t>
+          <t>Store contact person.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>outlet_status</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Store contact person.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>outlet_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Outlet status from the customer master, e.g. ACTIVE.</t>
         </is>

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -445,70 +445,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>HOS</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>State_CD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Cust_CD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>Cust_name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>CONT_PR</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>MOBILE_NO</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>ADDR_1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>ADDR_2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>ADDR_3</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>outlet_status</t>
+          <t>ADDR_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ADDR_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ADDR_POSTAL</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>SUB_CHANNEL</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LATITUDE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LONGITUDE</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>CUST_STATUS</t>
         </is>
       </c>
     </row>
@@ -524,10 +566,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
@@ -552,41 +594,41 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>HOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
+          <t>Head of sales / territory owner. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>State_CD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store name.</t>
+          <t>State code. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Cust_CD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -596,14 +638,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full store address.</t>
+          <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>pincode</t>
+          <t>Cust_name</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -613,48 +655,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PIN code.</t>
+          <t>Store name.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>lat</t>
+          <t>CONT_PR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latitude (decimal), between -90 and 90.</t>
+          <t>Contact person at the outlet.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>MOBILE_NO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Longitude (decimal), between -180 and 180.</t>
+          <t>Contact phone at the outlet.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>contact_no</t>
+          <t>ADDR_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -664,48 +706,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Store contact phone.</t>
+          <t>Address line 1. At least one ADDR_ line must have a real value.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>ADDR_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store contact email. Must be a valid address.</t>
+          <t>Address line 2.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>ADDR_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store contact person.</t>
+          <t>Address line 3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>outlet_status</t>
+          <t>ADDR_4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -715,7 +757,126 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Outlet status from the customer master, e.g. ACTIVE.</t>
+          <t>Address line 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ADDR_5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Address line 5. ADDR_1-ADDR_5 are joined into one address; blanks, '-' and 'NA' are dropped, and repeated lines are not duplicated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ADDR_POSTAL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PIN code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sales channel. Kept as source data; no field of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SUB_CHANNEL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sales sub-channel. Kept as source data; no field of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>LATITUDE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Latitude (decimal), between -90 and 90. A file spelling this LATTITUDE is also accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>LONGITUDE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Longitude (decimal), between -180 and 180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CUST_STATUS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Outlet status, e.g. ACTIVE. Stored as the store's outlet status.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Outlet status, e.g. ACTIVE. Stored as the store's outlet status.</t>
+          <t>Outlet status, e.g. ACTIVE. A store already marked INACTIVE/Closed is frozen: its row is rejected rather than updated, unless this row sets the status back to ACTIVE.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -475,17 +475,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>State_CD</t>
+          <t>STATE_CD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cust_CD</t>
+          <t>CUST_CD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cust_name</t>
+          <t>CUST_NAME</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>State_CD</t>
+          <t>STATE_CD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cust_CD</t>
+          <t>CUST_CD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Cust_name</t>
+          <t>CUST_NAME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/docs/bulk-templates/stores_template.xlsx
+++ b/docs/bulk-templates/stores_template.xlsx
@@ -73,10 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -566,321 +569,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>HOS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Head of sales / territory owner. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>STATE_CD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>State code. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CUST_CD</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Customer Code — the store's identifier and the key that decides update vs. create. An existing code updates that store in place and its tasks stay attached; a new code creates one. Must be unique.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CUST_NAME</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Store name.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CONT_PR</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Contact person at the outlet.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>MOBILE_NO</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Contact phone at the outlet.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ADDR_1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Address line 1. At least one ADDR_ line must have a real value.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>ADDR_2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Address line 2.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ADDR_3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Address line 3.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>ADDR_4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Address line 4.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>ADDR_5</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Address line 5. ADDR_1-ADDR_5 are joined into one address; blanks, '-' and 'NA' are dropped, and repeated lines are not duplicated.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>ADDR_POSTAL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>PIN code.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CHANNEL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sales channel. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SUB_CHANNEL</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Sales sub-channel. Kept as source data; no field of its own.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>LATITUDE</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Latitude (decimal), between -90 and 90. A file spelling this LATTITUDE is also accepted.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>LONGITUDE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Longitude (decimal), between -180 and 180.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CUST_STATUS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Outlet status, e.g. ACTIVE. A store already marked INACTIVE/Closed is frozen: its row is rejected rather than updated, unless this row sets the status back to ACTIVE.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>